--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.16719669375635</v>
+        <v>9.614669462735408</v>
       </c>
       <c r="D2" t="n">
-        <v>24.24972953902885</v>
+        <v>3.940581050092189</v>
       </c>
       <c r="E2" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F2" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.97761738850261</v>
+        <v>2.271362825631674</v>
       </c>
       <c r="D3" t="n">
-        <v>24.76859555200526</v>
+        <v>4.024896777200856</v>
       </c>
       <c r="E3" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F3" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.77766890269039</v>
+        <v>4.351371196687189</v>
       </c>
       <c r="D4" t="n">
-        <v>26.86829790103507</v>
+        <v>4.3660984089182</v>
       </c>
       <c r="E4" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F4" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.17931898756572</v>
+        <v>3.929139335479429</v>
       </c>
       <c r="D5" t="n">
-        <v>21.38262290279722</v>
+        <v>3.474676221704548</v>
       </c>
       <c r="E5" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F5" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.19204230108446</v>
+        <v>4.093706873926224</v>
       </c>
       <c r="D6" t="n">
-        <v>25.95700709762162</v>
+        <v>4.218013653363513</v>
       </c>
       <c r="E6" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F6" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.49113527347649</v>
+        <v>3.65480948193993</v>
       </c>
       <c r="D7" t="n">
-        <v>20.90163619345018</v>
+        <v>3.396515881435654</v>
       </c>
       <c r="E7" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F7" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.96102889805857</v>
+        <v>3.243667195934517</v>
       </c>
       <c r="D8" t="n">
-        <v>19.31521820536821</v>
+        <v>3.138722958372335</v>
       </c>
       <c r="E8" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F8" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.51798412566197</v>
+        <v>2.19667242042007</v>
       </c>
       <c r="D9" t="n">
-        <v>12.23432706606589</v>
+        <v>1.988078148235706</v>
       </c>
       <c r="E9" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F9" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>8.03246042929586</v>
+        <v>1.305274819760577</v>
       </c>
       <c r="D10" t="n">
-        <v>8.052257795908707</v>
+        <v>1.308491891835165</v>
       </c>
       <c r="E10" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F10" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>8.724820870971081</v>
+        <v>1.417783391532801</v>
       </c>
       <c r="D11" t="n">
-        <v>8.070859026900346</v>
+        <v>1.311514591871306</v>
       </c>
       <c r="E11" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F11" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.0626900403196</v>
+        <v>2.935187131551936</v>
       </c>
       <c r="D12" t="n">
-        <v>21.39755841530498</v>
+        <v>3.47710324248706</v>
       </c>
       <c r="E12" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F12" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>14.4757297639818</v>
+        <v>2.352306086647042</v>
       </c>
       <c r="D13" t="n">
-        <v>13.79519087446284</v>
+        <v>2.241718517100212</v>
       </c>
       <c r="E13" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F13" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>25.60554621351967</v>
+        <v>4.160901259696947</v>
       </c>
       <c r="D14" t="n">
-        <v>26.2912420625606</v>
+        <v>4.272326835166098</v>
       </c>
       <c r="E14" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F14" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>21.46537844193129</v>
+        <v>3.488123996813835</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3899637039561694</v>
+        <v>0.06336910189287752</v>
       </c>
       <c r="E15" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F15" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>14.81064760581642</v>
+        <v>2.406730235945168</v>
       </c>
       <c r="D16" t="n">
-        <v>40.21744359559447</v>
+        <v>6.535334584284101</v>
       </c>
       <c r="E16" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F16" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>20.84006192539744</v>
+        <v>3.386510062877084</v>
       </c>
       <c r="D17" t="n">
-        <v>39.37423480226691</v>
+        <v>6.398313155368373</v>
       </c>
       <c r="E17" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F17" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>33.88194126647505</v>
+        <v>5.505815455802196</v>
       </c>
       <c r="D18" t="n">
-        <v>33.28548899335324</v>
+        <v>5.408891961419902</v>
       </c>
       <c r="E18" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F18" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>25.75456696718938</v>
+        <v>4.185117132168275</v>
       </c>
       <c r="D19" t="n">
-        <v>25.03118115893979</v>
+        <v>4.067566938327716</v>
       </c>
       <c r="E19" t="n">
-        <v>11.11769148558991</v>
+        <v>1.80662486640836</v>
       </c>
       <c r="F19" t="n">
-        <v>10.18469713313499</v>
+        <v>1.655013284134436</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
